--- a/Proyecto Interno/interno/output/sensibilidad_umbral/actual/coca_results.xlsx
+++ b/Proyecto Interno/interno/output/sensibilidad_umbral/actual/coca_results.xlsx
@@ -420,21 +420,21 @@
         </is>
       </c>
       <c r="B2">
-        <v>615.5112858433653</v>
+        <v>610.1280078255212</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1938.860550406601</v>
+        <v>1921.903224650392</v>
       </c>
       <c r="F2">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -458,21 +458,21 @@
         </is>
       </c>
       <c r="B3">
-        <v>610.1280078255213</v>
+        <v>615.5112858433652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1921.903224650393</v>
+        <v>1938.8605504066</v>
       </c>
       <c r="F3">
-        <v>882.3529411764709</v>
+        <v>882.3529411764705</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>817.0722755731049</v>
+        <v>818.1970626236806</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2573.777668055281</v>
+        <v>2577.320747264594</v>
       </c>
       <c r="F4">
-        <v>882.3529411764709</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -534,21 +534,21 @@
         </is>
       </c>
       <c r="B5">
-        <v>615.5112858433653</v>
+        <v>610.1280078255213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1938.860550406601</v>
+        <v>1921.903224650392</v>
       </c>
       <c r="F5">
-        <v>882.3529411764706</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -572,18 +572,18 @@
         </is>
       </c>
       <c r="B6">
-        <v>610.1280078255212</v>
+        <v>615.5112858433653</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1921.903224650392</v>
+        <v>1938.860550406601</v>
       </c>
       <c r="F6">
         <v>882.3529411764706</v>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>817.0722755731049</v>
+        <v>818.1970626236806</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2573.777668055281</v>
+        <v>2577.320747264594</v>
       </c>
       <c r="F7">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -648,21 +648,21 @@
         </is>
       </c>
       <c r="B8">
-        <v>615.5112858433653</v>
+        <v>610.1280078255212</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1938.860550406601</v>
+        <v>1921.903224650392</v>
       </c>
       <c r="F8">
-        <v>882.3529411764706</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="B9">
-        <v>610.1280078255212</v>
+        <v>615.5112858433653</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1921.903224650392</v>
+        <v>1938.860550406601</v>
       </c>
       <c r="F9">
-        <v>882.3529411764706</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>817.0722755731047</v>
+        <v>818.1970626236806</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -735,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>2573.77766805528</v>
+        <v>2577.320747264595</v>
       </c>
       <c r="F10">
-        <v>882.3529411764705</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -762,21 +762,21 @@
         </is>
       </c>
       <c r="B11">
-        <v>615.6131069443312</v>
+        <v>594.7921732203172</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1705.248306235797</v>
+        <v>1647.574319820278</v>
       </c>
       <c r="F11">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="B12">
-        <v>594.7921732203171</v>
+        <v>615.6131069443312</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>1647.574319820278</v>
+        <v>1705.248306235797</v>
       </c>
       <c r="F12">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>2219.870564462949</v>
       </c>
       <c r="F13">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -876,21 +876,21 @@
         </is>
       </c>
       <c r="B14">
-        <v>615.6131069443312</v>
+        <v>594.792173220317</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1705.248306235797</v>
+        <v>1647.574319820278</v>
       </c>
       <c r="F14">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="B15">
-        <v>594.7921732203171</v>
+        <v>615.613106944331</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1647.574319820278</v>
+        <v>1705.248306235797</v>
       </c>
       <c r="F15">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>801.3973156905955</v>
+        <v>801.3973156905953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>2219.870564462949</v>
       </c>
       <c r="F16">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -990,18 +990,18 @@
         </is>
       </c>
       <c r="B17">
-        <v>605.437683689053</v>
+        <v>584.9608976298987</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1671.008006981786</v>
+        <v>1614.49207745852</v>
       </c>
       <c r="F17">
         <v>760.3305785123969</v>
@@ -1028,21 +1028,21 @@
         </is>
       </c>
       <c r="B18">
-        <v>584.9608976298987</v>
+        <v>605.437683689053</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>1614.49207745852</v>
+        <v>1671.008006981786</v>
       </c>
       <c r="F18">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>788.1510790676106</v>
+        <v>788.1510790676105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="B20">
-        <v>615.1701373509227</v>
+        <v>596.8116493338341</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>1704.021280462056</v>
+        <v>1653.168268654721</v>
       </c>
       <c r="F20">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="B21">
-        <v>596.8116493338342</v>
+        <v>615.1701373509227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1653.168268654721</v>
+        <v>1704.021280462056</v>
       </c>
       <c r="F21">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>804.2683015495813</v>
+        <v>804.6241424658284</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2227.82319529234</v>
+        <v>2228.808874630345</v>
       </c>
       <c r="F22">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1218,21 +1218,21 @@
         </is>
       </c>
       <c r="B23">
-        <v>615.1701373509227</v>
+        <v>596.811649333834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>1704.021280462056</v>
+        <v>1653.16826865472</v>
       </c>
       <c r="F23">
-        <v>775.9103641456584</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="B24">
-        <v>596.8116493338342</v>
+        <v>615.1701373509226</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>1653.168268654721</v>
+        <v>1704.021280462056</v>
       </c>
       <c r="F24">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>804.2683015495813</v>
+        <v>804.6241424658282</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>2227.82319529234</v>
+        <v>2228.808874630344</v>
       </c>
       <c r="F25">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="B26">
-        <v>605.0020359071058</v>
+        <v>586.9469939729444</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1669.805619103612</v>
+        <v>1619.973703365326</v>
       </c>
       <c r="F26">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="B27">
-        <v>586.9469939729444</v>
+        <v>605.0020359071058</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>1619.973703365326</v>
+        <v>1669.805619103612</v>
       </c>
       <c r="F27">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>790.9746106148775</v>
+        <v>791.3245698630874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2183.089925297062</v>
+        <v>2184.055812822121</v>
       </c>
       <c r="F28">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1446,21 +1446,21 @@
         </is>
       </c>
       <c r="B29">
-        <v>616.8964876981092</v>
+        <v>603.9331682446305</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>1708.803270923763</v>
+        <v>1672.894876037626</v>
       </c>
       <c r="F29">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="B30">
-        <v>603.9331682446307</v>
+        <v>616.8964876981092</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>1672.894876037627</v>
+        <v>1708.803270923763</v>
       </c>
       <c r="F30">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>815.3976236620928</v>
+        <v>815.3976236620925</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>2258.651417543997</v>
       </c>
       <c r="F31">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="B32">
-        <v>616.8964876981092</v>
+        <v>603.9331682446307</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>1708.803270923763</v>
+        <v>1672.894876037627</v>
       </c>
       <c r="F32">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="B33">
-        <v>603.9331682446306</v>
+        <v>616.8964876981094</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>1672.894876037627</v>
+        <v>1708.803270923763</v>
       </c>
       <c r="F33">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1674,18 +1674,18 @@
         </is>
       </c>
       <c r="B35">
-        <v>606.6998515378099</v>
+        <v>593.950801827364</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>1674.491590244355</v>
+        <v>1639.304213043524</v>
       </c>
       <c r="F35">
         <v>760.3305785123968</v>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="B36">
-        <v>593.950801827364</v>
+        <v>606.6998515378099</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36">
-        <v>1639.304213043524</v>
+        <v>1674.491590244355</v>
       </c>
       <c r="F36">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>801.9199769899918</v>
+        <v>801.9199769899921</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>2213.299136492377</v>
+        <v>2213.299136492378</v>
       </c>
       <c r="F37">
-        <v>760.3305785123965</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="B38">
-        <v>616.0453333603427</v>
+        <v>611.5290386663376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>1940.54280008508</v>
+        <v>1926.316471798963</v>
       </c>
       <c r="F38">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="B39">
-        <v>611.5290386663376</v>
+        <v>616.0453333603427</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39">
-        <v>1926.316471798963</v>
+        <v>1940.54280008508</v>
       </c>
       <c r="F39">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>772.0347671759838</v>
+        <v>772.0347671759837</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>2431.909516604349</v>
       </c>
       <c r="F40">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="B41">
-        <v>616.0453333603427</v>
+        <v>611.5290386663376</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
-        <v>1940.54280008508</v>
+        <v>1926.316471798963</v>
       </c>
       <c r="F41">
-        <v>882.3529411764708</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="B42">
-        <v>611.5290386663376</v>
+        <v>616.0453333603427</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>1926.316471798963</v>
+        <v>1940.54280008508</v>
       </c>
       <c r="F42">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>2431.909516604349</v>
       </c>
       <c r="F43">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="B44">
-        <v>616.0453333603427</v>
+        <v>611.5290386663376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44">
-        <v>1940.54280008508</v>
+        <v>1926.316471798963</v>
       </c>
       <c r="F44">
-        <v>882.3529411764708</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2054,21 +2054,21 @@
         </is>
       </c>
       <c r="B45">
-        <v>611.5290386663376</v>
+        <v>616.0453333603427</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>1926.316471798963</v>
+        <v>1940.54280008508</v>
       </c>
       <c r="F45">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>2431.909516604349</v>
       </c>
       <c r="F46">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2126,25 +2126,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B47">
-        <v>622.6067439330452</v>
+        <v>596.8116493338341</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>2042.150120100388</v>
+        <v>1653.168268654721</v>
       </c>
       <c r="F47">
-        <v>929.1784702549575</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2164,25 +2164,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B48">
-        <v>603.5743875699116</v>
+        <v>615.6307580066247</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>1979.72399122931</v>
+        <v>1705.29719967835</v>
       </c>
       <c r="F48">
-        <v>929.1784702549575</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2202,11 +2202,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B49">
-        <v>813.3818233801713</v>
+        <v>804.6241424658284</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>2667.892380686962</v>
+        <v>2228.808874630345</v>
       </c>
       <c r="F49">
-        <v>929.1784702549575</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2240,25 +2240,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B50">
-        <v>622.6067439330452</v>
+        <v>596.8116493338342</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>2042.150120100389</v>
+        <v>1653.168268654721</v>
       </c>
       <c r="F50">
-        <v>929.1784702549576</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2278,25 +2278,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B51">
-        <v>603.5743875699116</v>
+        <v>615.6307580066247</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51">
-        <v>1979.72399122931</v>
+        <v>1705.29719967835</v>
       </c>
       <c r="F51">
-        <v>929.1784702549577</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2316,11 +2316,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B52">
-        <v>813.3818233801713</v>
+        <v>804.6241424658284</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>2667.892380686962</v>
+        <v>2228.808874630345</v>
       </c>
       <c r="F52">
-        <v>929.1784702549576</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2354,25 +2354,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco cáscara</t>
         </is>
       </c>
       <c r="B53">
-        <v>622.6067439330452</v>
+        <v>586.9469939729443</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53">
-        <v>2042.150120100389</v>
+        <v>1619.973703365326</v>
       </c>
       <c r="F53">
-        <v>929.1784702549576</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2392,25 +2392,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco cáscara</t>
         </is>
       </c>
       <c r="B54">
-        <v>603.5743875699116</v>
+        <v>605.4550429982506</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54">
-        <v>1979.72399122931</v>
+        <v>1671.055918675172</v>
       </c>
       <c r="F54">
-        <v>929.1784702549577</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2430,11 +2430,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco cáscara</t>
         </is>
       </c>
       <c r="B55">
-        <v>813.3818233801713</v>
+        <v>791.3245698630874</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>2667.892380686962</v>
+        <v>2184.055812822121</v>
       </c>
       <c r="F55">
-        <v>929.1784702549576</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2472,21 +2472,21 @@
         </is>
       </c>
       <c r="B56">
-        <v>616.8938163500695</v>
+        <v>593.6738291541036</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1708.795871289693</v>
+        <v>1644.476506756867</v>
       </c>
       <c r="F56">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2510,18 +2510,18 @@
         </is>
       </c>
       <c r="B57">
-        <v>593.5728658088276</v>
+        <v>616.8938163500695</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1644.196838290452</v>
+        <v>1708.795871289693</v>
       </c>
       <c r="F57">
         <v>775.9103641456584</v>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>796.4613521440849</v>
+        <v>796.856189960668</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>2206.197945439115</v>
+        <v>2207.29164619105</v>
       </c>
       <c r="F58">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2586,21 +2586,21 @@
         </is>
       </c>
       <c r="B59">
-        <v>616.8938163500694</v>
+        <v>593.6738291541037</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1708.795871289692</v>
+        <v>1644.476506756867</v>
       </c>
       <c r="F59">
-        <v>775.910364145658</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2624,21 +2624,21 @@
         </is>
       </c>
       <c r="B60">
-        <v>593.5728658088276</v>
+        <v>616.8938163500696</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60">
-        <v>1644.196838290452</v>
+        <v>1708.795871289693</v>
       </c>
       <c r="F60">
-        <v>775.9103641456581</v>
+        <v>775.9103641456585</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>796.4613521440849</v>
+        <v>796.8561899606681</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>2206.197945439115</v>
+        <v>2207.29164619105</v>
       </c>
       <c r="F61">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2700,21 +2700,21 @@
         </is>
       </c>
       <c r="B62">
-        <v>606.6972243442833</v>
+        <v>583.861038589573</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D62">
         <v>1</v>
       </c>
       <c r="E62">
-        <v>1674.484339190222</v>
+        <v>1611.456466507221</v>
       </c>
       <c r="F62">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="B63">
-        <v>583.7617440599213</v>
+        <v>606.6972243442833</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63">
-        <v>1611.182413605383</v>
+        <v>1674.484339190222</v>
       </c>
       <c r="F63">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>783.2967016954223</v>
+        <v>783.6850132671034</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>2161.898896679366</v>
+        <v>2162.970636617205</v>
       </c>
       <c r="F64">
         <v>760.3305785123969</v>
@@ -2810,25 +2810,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B65">
-        <v>580.0376974665129</v>
+        <v>591.8499376767588</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>1711.111207526213</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F65">
-        <v>776.3157894736839</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B66">
-        <v>556.027441448955</v>
+        <v>617.4070729335432</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66">
-        <v>1640.280952274417</v>
+        <v>1710.217592025914</v>
       </c>
       <c r="F66">
-        <v>776.315789473684</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2886,11 +2886,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B67">
-        <v>743.6826264044637</v>
+        <v>791.6409828519764</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>2193.863747893167</v>
+        <v>2192.845522499974</v>
       </c>
       <c r="F67">
-        <v>776.3157894736839</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2924,25 +2924,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B68">
-        <v>624.4031870744332</v>
+        <v>591.8499376767587</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68">
-        <v>2048.042453604141</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F68">
-        <v>929.1784702549573</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2962,25 +2962,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B69">
-        <v>598.556452551283</v>
+        <v>617.4070729335432</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1963.265164368208</v>
+        <v>1710.217592025914</v>
       </c>
       <c r="F69">
-        <v>929.1784702549575</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3000,11 +3000,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B70">
-        <v>800.5648669509807</v>
+        <v>791.6409828519766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>2625.852763599216</v>
+        <v>2192.845522499975</v>
       </c>
       <c r="F70">
-        <v>929.1784702549573</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="B71">
-        <v>607.2019973478647</v>
+        <v>582.0672940787958</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>1675.877512680107</v>
+        <v>1606.505731657477</v>
       </c>
       <c r="F71">
-        <v>760.3305785123966</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         </is>
       </c>
       <c r="B72">
-        <v>582.0672940787958</v>
+        <v>607.201997347865</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1606.505731657476</v>
+        <v>1675.877512680107</v>
       </c>
       <c r="F72">
-        <v>760.3305785123968</v>
+        <v>760.330578512397</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>778.5107383848381</v>
+        <v>778.5560079288034</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3129,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>2148.689637942153</v>
+        <v>2148.814581883497</v>
       </c>
       <c r="F73">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="B74">
-        <v>616.4841953041379</v>
+        <v>595.6704937585603</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74">
-        <v>1707.661220992462</v>
+        <v>1650.007267711212</v>
       </c>
       <c r="F74">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3194,21 +3194,21 @@
         </is>
       </c>
       <c r="B75">
-        <v>595.4824100601712</v>
+        <v>616.4841953041379</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75">
-        <v>1649.486275866674</v>
+        <v>1707.661220992462</v>
       </c>
       <c r="F75">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>753.6439489665659</v>
+        <v>753.6439489665657</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>2087.593738637388</v>
+        <v>2087.593738637387</v>
       </c>
       <c r="F76">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3270,21 +3270,21 @@
         </is>
       </c>
       <c r="B77">
-        <v>616.4841953041379</v>
+        <v>595.6704937585603</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
       <c r="E77">
-        <v>1707.661220992462</v>
+        <v>1650.007267711212</v>
       </c>
       <c r="F77">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="B78">
-        <v>595.4824100601712</v>
+        <v>616.4841953041379</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
       <c r="E78">
-        <v>1649.486275866674</v>
+        <v>1707.661220992462</v>
       </c>
       <c r="F78">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>753.643948966566</v>
+        <v>753.6439489665659</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="B80">
-        <v>606.2943738941522</v>
+        <v>585.8247004732949</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
-        <v>1673.372471947861</v>
+        <v>1616.876173306294</v>
       </c>
       <c r="F80">
-        <v>760.3305785123971</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3422,21 +3422,21 @@
         </is>
       </c>
       <c r="B81">
-        <v>585.6397255963667</v>
+        <v>606.2943738941522</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>1616.365642645972</v>
+        <v>1673.37247194786</v>
       </c>
       <c r="F81">
-        <v>760.330578512397</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>2045.676186765115</v>
       </c>
       <c r="F82">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3498,18 +3498,18 @@
         </is>
       </c>
       <c r="B83">
-        <v>615.2424032070854</v>
+        <v>641.0918539008137</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>1938.013570102319</v>
+        <v>2019.439339787563</v>
       </c>
       <c r="F83">
         <v>882.3529411764706</v>
@@ -3536,21 +3536,21 @@
         </is>
       </c>
       <c r="B84">
-        <v>640.8797137303673</v>
+        <v>615.2424032070855</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>2018.771098250657</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F84">
-        <v>882.3529411764706</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B85">
-        <v>801.1695975506458</v>
+        <v>801.431630700243</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>2523.684232284534</v>
+        <v>2524.509636705765</v>
       </c>
       <c r="F85">
         <v>882.3529411764707</v>
@@ -3608,25 +3608,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B86">
-        <v>578.0040472234987</v>
+        <v>641.0918539008137</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>1895.853274893075</v>
+        <v>2019.439339787563</v>
       </c>
       <c r="F86">
-        <v>863.157894736842</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3646,25 +3646,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B87">
-        <v>602.0896257940556</v>
+        <v>615.2424032070855</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>1974.853972604502</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F87">
-        <v>863.157894736842</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3684,11 +3684,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B88">
-        <v>752.6777534883697</v>
+        <v>801.431630700243</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>2468.783031441852</v>
+        <v>2524.509636705765</v>
       </c>
       <c r="F88">
-        <v>863.157894736842</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3726,18 +3726,18 @@
         </is>
       </c>
       <c r="B89">
-        <v>615.2424032070854</v>
+        <v>641.0918539008137</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>1938.013570102319</v>
+        <v>2019.439339787563</v>
       </c>
       <c r="F89">
         <v>882.3529411764707</v>
@@ -3764,18 +3764,18 @@
         </is>
       </c>
       <c r="B90">
-        <v>640.8797137303673</v>
+        <v>615.2424032070855</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90">
-        <v>2018.771098250657</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F90">
         <v>882.3529411764707</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="B91">
-        <v>801.1695975506458</v>
+        <v>801.431630700243</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>2523.684232284535</v>
+        <v>2524.509636705765</v>
       </c>
       <c r="F91">
-        <v>882.3529411764709</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3840,21 +3840,21 @@
         </is>
       </c>
       <c r="B92">
-        <v>617.4141424533667</v>
+        <v>582.568471080514</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>1710.237174595826</v>
+        <v>1613.714664893024</v>
       </c>
       <c r="F92">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="B93">
-        <v>582.5374811456834</v>
+        <v>617.4141424533667</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>1613.628822773543</v>
+        <v>1710.237174595826</v>
       </c>
       <c r="F93">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="B94">
-        <v>774.4226300474685</v>
+        <v>774.7826439545263</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>2145.150685231488</v>
+        <v>2146.147923754038</v>
       </c>
       <c r="F94">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         </is>
       </c>
       <c r="B95">
-        <v>617.4141424533667</v>
+        <v>582.568471080514</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>1710.237174595826</v>
+        <v>1613.714664893024</v>
       </c>
       <c r="F95">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3992,21 +3992,21 @@
         </is>
       </c>
       <c r="B96">
-        <v>582.5374811456834</v>
+        <v>617.4141424533667</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>1613.628822773543</v>
+        <v>1710.237174595826</v>
       </c>
       <c r="F96">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>774.4226300474685</v>
+        <v>774.7826439545263</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>2145.150685231488</v>
+        <v>2146.147923754038</v>
       </c>
       <c r="F97">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4068,21 +4068,21 @@
         </is>
       </c>
       <c r="B98">
-        <v>607.208950016121</v>
+        <v>572.9392401535633</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>1675.896702044494</v>
+        <v>1581.312302823835</v>
       </c>
       <c r="F98">
-        <v>760.3305785123969</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4106,18 +4106,18 @@
         </is>
       </c>
       <c r="B99">
-        <v>572.9087624490606</v>
+        <v>607.208950016121</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>1581.228184359407</v>
+        <v>1675.896702044494</v>
       </c>
       <c r="F99">
         <v>760.3305785123969</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>761.6222559970975</v>
+        <v>761.9763192610632</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>2102.077426551989</v>
+        <v>2103.054641160534</v>
       </c>
       <c r="F100">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4182,21 +4182,21 @@
         </is>
       </c>
       <c r="B101">
-        <v>615.7584096167852</v>
+        <v>591.8499376767588</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>1705.650794638495</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F101">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4220,21 +4220,21 @@
         </is>
       </c>
       <c r="B102">
-        <v>591.8499376767588</v>
+        <v>615.7584096167852</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>1639.424327364622</v>
+        <v>1705.650794638495</v>
       </c>
       <c r="F102">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>791.5949524753396</v>
+        <v>791.6409828519766</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>2192.718018356691</v>
+        <v>2192.845522499975</v>
       </c>
       <c r="F103">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="B104">
-        <v>615.7584096167852</v>
+        <v>591.8499376767587</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>1705.650794638495</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F104">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4334,21 +4334,21 @@
         </is>
       </c>
       <c r="B105">
-        <v>591.8499376767588</v>
+        <v>615.7584096167851</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>1639.424327364622</v>
+        <v>1705.650794638495</v>
       </c>
       <c r="F105">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>791.5949524753396</v>
+        <v>791.6409828519763</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>2192.718018356691</v>
+        <v>2192.845522499974</v>
       </c>
       <c r="F106">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4410,21 +4410,21 @@
         </is>
       </c>
       <c r="B107">
-        <v>605.5805846644415</v>
+        <v>582.0672940787958</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>1671.402413673859</v>
+        <v>1606.505731657477</v>
       </c>
       <c r="F107">
-        <v>760.3305785123966</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="B108">
-        <v>582.0672940787958</v>
+        <v>605.5805846644417</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>1606.505731657476</v>
+        <v>1671.402413673859</v>
       </c>
       <c r="F108">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>778.5107383848381</v>
+        <v>778.5560079288033</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>2148.689637942153</v>
+        <v>2148.814581883497</v>
       </c>
       <c r="F109">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4524,21 +4524,21 @@
         </is>
       </c>
       <c r="B110">
-        <v>615.9968081322152</v>
+        <v>593.4848694406776</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>1706.311158526236</v>
+        <v>1643.953088350677</v>
       </c>
       <c r="F110">
-        <v>775.910364145658</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4562,21 +4562,21 @@
         </is>
       </c>
       <c r="B111">
-        <v>593.4695950179541</v>
+        <v>615.9968081322152</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>1643.910778199733</v>
+        <v>1706.311158526236</v>
       </c>
       <c r="F111">
-        <v>775.9103641456581</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>795.9937678155779</v>
+        <v>795.9937678155778</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>2204.902736849151</v>
+        <v>2204.90273684915</v>
       </c>
       <c r="F112">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4638,21 +4638,21 @@
         </is>
       </c>
       <c r="B113">
-        <v>615.9968081322152</v>
+        <v>593.4848694406776</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>1706.311158526236</v>
+        <v>1643.953088350677</v>
       </c>
       <c r="F113">
-        <v>775.910364145658</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="B114">
-        <v>593.4695950179541</v>
+        <v>615.9968081322152</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>1643.910778199733</v>
+        <v>1706.311158526236</v>
       </c>
       <c r="F114">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>2204.902736849151</v>
       </c>
       <c r="F115">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="B116">
-        <v>605.8150427085421</v>
+        <v>583.6752021771953</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[10, 14)</t>
+          <t>[31,51)</t>
         </is>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>1672.049517875576</v>
+        <v>1610.943558009059</v>
       </c>
       <c r="F116">
-        <v>760.3305785123966</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4790,18 +4790,18 @@
         </is>
       </c>
       <c r="B117">
-        <v>583.6601802242689</v>
+        <v>605.8150427085423</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>[31,51)</t>
+          <t>[10, 14)</t>
         </is>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>1610.902097418982</v>
+        <v>1672.049517875577</v>
       </c>
       <c r="F117">
         <v>760.3305785123968</v>
